--- a/data/Lineups.xlsx
+++ b/data/Lineups.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\Radical_stats\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BEDC46D-E6CC-4CC5-9AD5-4A3B31D90A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93E3638-7FB0-4B32-8B57-086F6FFEE839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{2F8EDDAE-8367-4C64-A34D-358EA07D1A8E}"/>
   </bookViews>
@@ -1616,7 +1616,7 @@
         <v>0</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O19">
         <v>0</v>
